--- a/RET_KPI_Sales_Database.xlsx
+++ b/RET_KPI_Sales_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/30722571119c7a42/Documents/Fede/AI Test/Retail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{013E9734-E5F4-485C-9734-B8A02A00E18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F652607B-6408-4893-94A0-FAB8FDB038DB}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{013E9734-E5F4-485C-9734-B8A02A00E18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0811452-6F43-4E88-97E3-1F301BD90DD6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -283,6 +283,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -303,6 +304,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -695,10 +700,10 @@
         <v>19</v>
       </c>
       <c r="F2" s="3">
-        <v>24261</v>
+        <v>24271</v>
       </c>
       <c r="G2" s="3">
-        <v>2525</v>
+        <v>2535</v>
       </c>
       <c r="H2" s="3">
         <v>861409.64000000048</v>
@@ -716,8 +721,8 @@
         <v>575672.19999999972</v>
       </c>
       <c r="M2" s="4"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="3"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
       <c r="Q2" s="5"/>
     </row>
     <row r="3" spans="1:17">
@@ -737,10 +742,10 @@
         <v>20</v>
       </c>
       <c r="F3" s="3">
-        <v>18880</v>
+        <v>18890</v>
       </c>
       <c r="G3" s="3">
-        <v>1971</v>
+        <v>1981</v>
       </c>
       <c r="H3" s="3">
         <v>783742.96000000089</v>
@@ -758,8 +763,8 @@
         <v>527519.27240000037</v>
       </c>
       <c r="M3" s="4"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="3"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
       <c r="Q3" s="5"/>
     </row>
     <row r="4" spans="1:17">
@@ -779,10 +784,10 @@
         <v>21</v>
       </c>
       <c r="F4" s="3">
-        <v>19615</v>
+        <v>19625</v>
       </c>
       <c r="G4" s="3">
-        <v>2504</v>
+        <v>2514</v>
       </c>
       <c r="H4" s="3">
         <v>1052789.2400000005</v>
@@ -800,8 +805,8 @@
         <v>714342.35479999986</v>
       </c>
       <c r="M4" s="4"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="3"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17">
@@ -821,10 +826,10 @@
         <v>22</v>
       </c>
       <c r="F5" s="3">
-        <v>18408</v>
+        <v>18418</v>
       </c>
       <c r="G5" s="3">
-        <v>2435</v>
+        <v>2445</v>
       </c>
       <c r="H5" s="3">
         <v>952224.7200000002</v>
@@ -842,8 +847,8 @@
         <v>623385.2804000004</v>
       </c>
       <c r="M5" s="4"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="3"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
       <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="1:17">
@@ -863,10 +868,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="3">
-        <v>17925</v>
+        <v>17935</v>
       </c>
       <c r="G6" s="3">
-        <v>2300</v>
+        <v>2310</v>
       </c>
       <c r="H6" s="3">
         <v>917137.20000000112</v>
@@ -884,8 +889,8 @@
         <v>610538.66999999946</v>
       </c>
       <c r="M6" s="4"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="3"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
       <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="1:17">
@@ -905,10 +910,10 @@
         <v>24</v>
       </c>
       <c r="F7" s="3">
-        <v>26123</v>
+        <v>26133</v>
       </c>
       <c r="G7" s="3">
-        <v>3329</v>
+        <v>3339</v>
       </c>
       <c r="H7" s="3">
         <v>1342448.2399999998</v>
@@ -926,8 +931,8 @@
         <v>879563.09239999985</v>
       </c>
       <c r="M7" s="4"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="3"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
       <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17">
@@ -947,10 +952,10 @@
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>26887</v>
+        <v>26897</v>
       </c>
       <c r="G8" s="3">
-        <v>2857</v>
+        <v>2867</v>
       </c>
       <c r="H8" s="3">
         <v>1247823.4799999988</v>
@@ -968,8 +973,8 @@
         <v>848367.50719999976</v>
       </c>
       <c r="M8" s="4"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="3"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17">
@@ -989,10 +994,10 @@
         <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>23971</v>
+        <v>23981</v>
       </c>
       <c r="G9" s="3">
-        <v>2764</v>
+        <v>2774</v>
       </c>
       <c r="H9" s="3">
         <v>1075411.5600000008</v>
@@ -1010,8 +1015,8 @@
         <v>713519.26639999927</v>
       </c>
       <c r="M9" s="4"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="3"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="31"/>
       <c r="Q9" s="5"/>
     </row>
     <row r="10" spans="1:17">
@@ -1031,10 +1036,10 @@
         <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>18553</v>
+        <v>18563</v>
       </c>
       <c r="G10" s="3">
-        <v>2312</v>
+        <v>2322</v>
       </c>
       <c r="H10" s="3">
         <v>953489.20000000042</v>
@@ -1052,8 +1057,8 @@
         <v>652332.39719999942</v>
       </c>
       <c r="M10" s="4"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="3"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
       <c r="Q10" s="5"/>
     </row>
     <row r="11" spans="1:17">
@@ -1073,10 +1078,10 @@
         <v>28</v>
       </c>
       <c r="F11" s="3">
-        <v>17765</v>
+        <v>17775</v>
       </c>
       <c r="G11" s="3">
-        <v>2221</v>
+        <v>2231</v>
       </c>
       <c r="H11" s="3">
         <v>858679.0000000007</v>
@@ -1094,8 +1099,8 @@
         <v>570616.68039999972</v>
       </c>
       <c r="M11" s="4"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="3"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
       <c r="Q11" s="5"/>
     </row>
     <row r="12" spans="1:17">
@@ -1115,10 +1120,10 @@
         <v>29</v>
       </c>
       <c r="F12" s="3">
-        <v>21112</v>
+        <v>21122</v>
       </c>
       <c r="G12" s="3">
-        <v>3030</v>
+        <v>3040</v>
       </c>
       <c r="H12" s="3">
         <v>1051650.7200000004</v>
@@ -1136,8 +1141,8 @@
         <v>712471.53759999946</v>
       </c>
       <c r="M12" s="4"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="3"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
       <c r="Q12" s="5"/>
     </row>
     <row r="13" spans="1:17">
@@ -1157,10 +1162,10 @@
         <v>30</v>
       </c>
       <c r="F13" s="3">
-        <v>34116</v>
+        <v>34126</v>
       </c>
       <c r="G13" s="3">
-        <v>5203</v>
+        <v>5213</v>
       </c>
       <c r="H13" s="3">
         <v>1705548.6399999985</v>
@@ -1178,8 +1183,8 @@
         <v>1155378.5900000003</v>
       </c>
       <c r="M13" s="4"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="3"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
       <c r="Q13" s="5"/>
     </row>
     <row r="14" spans="1:17">
@@ -1199,10 +1204,10 @@
         <v>19</v>
       </c>
       <c r="F14" s="3">
-        <v>19872</v>
+        <v>19882</v>
       </c>
       <c r="G14" s="3">
-        <v>2131</v>
+        <v>2141</v>
       </c>
       <c r="H14" s="3">
         <v>899339.76000000106</v>
@@ -1220,8 +1225,8 @@
         <v>604332.64079999959</v>
       </c>
       <c r="M14" s="4"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="3"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
       <c r="Q14" s="5"/>
     </row>
     <row r="15" spans="1:17">
@@ -1241,10 +1246,10 @@
         <v>20</v>
       </c>
       <c r="F15" s="3">
-        <v>17146</v>
+        <v>17156</v>
       </c>
       <c r="G15" s="3">
-        <v>2500</v>
+        <v>2510</v>
       </c>
       <c r="H15" s="3">
         <v>981669.72</v>
@@ -1262,8 +1267,8 @@
         <v>651963.11840000039</v>
       </c>
       <c r="M15" s="4"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="3"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
       <c r="Q15" s="5"/>
     </row>
     <row r="16" spans="1:17">
@@ -1283,10 +1288,10 @@
         <v>21</v>
       </c>
       <c r="F16" s="3">
-        <v>18647</v>
+        <v>18657</v>
       </c>
       <c r="G16" s="3">
-        <v>2746</v>
+        <v>2756</v>
       </c>
       <c r="H16" s="3">
         <v>1018951.84</v>
@@ -1304,8 +1309,8 @@
         <v>701716.52279999957</v>
       </c>
       <c r="M16" s="4"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="3"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
       <c r="Q16" s="5"/>
     </row>
     <row r="17" spans="1:17">
@@ -1325,10 +1330,10 @@
         <v>22</v>
       </c>
       <c r="F17" s="3">
-        <v>18886</v>
+        <v>18896</v>
       </c>
       <c r="G17" s="3">
-        <v>2588</v>
+        <v>2598</v>
       </c>
       <c r="H17" s="3">
         <v>948536.68000000075</v>
@@ -1346,8 +1351,8 @@
         <v>642204.80160000001</v>
       </c>
       <c r="M17" s="4"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="3"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
       <c r="Q17" s="5"/>
     </row>
     <row r="18" spans="1:17">
@@ -1367,10 +1372,10 @@
         <v>23</v>
       </c>
       <c r="F18" s="3">
-        <v>13937</v>
+        <v>13947</v>
       </c>
       <c r="G18" s="3">
-        <v>1928</v>
+        <v>1938</v>
       </c>
       <c r="H18" s="3">
         <v>862432.92000000016</v>
@@ -1388,8 +1393,8 @@
         <v>584096.94999999995</v>
       </c>
       <c r="M18" s="4"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="3"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
       <c r="Q18" s="5"/>
     </row>
     <row r="19" spans="1:17">
@@ -1409,10 +1414,10 @@
         <v>24</v>
       </c>
       <c r="F19" s="3">
-        <v>19550</v>
+        <v>19560</v>
       </c>
       <c r="G19" s="3">
-        <v>2961</v>
+        <v>2971</v>
       </c>
       <c r="H19" s="3">
         <v>1073873.4400000009</v>
@@ -1430,8 +1435,8 @@
         <v>733857.06199999957</v>
       </c>
       <c r="M19" s="4"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="3"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
       <c r="Q19" s="5"/>
     </row>
     <row r="20" spans="1:17">
@@ -1451,10 +1456,10 @@
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>20357</v>
+        <v>20367</v>
       </c>
       <c r="G20" s="3">
-        <v>2530</v>
+        <v>2540</v>
       </c>
       <c r="H20" s="3">
         <v>972703.63999999955</v>
@@ -1472,8 +1477,8 @@
         <v>648440.47400000039</v>
       </c>
       <c r="M20" s="4"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="3"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
       <c r="Q20" s="5"/>
     </row>
     <row r="21" spans="1:17">
@@ -1493,10 +1498,10 @@
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>24141</v>
+        <v>24151</v>
       </c>
       <c r="G21" s="3">
-        <v>3423</v>
+        <v>3433</v>
       </c>
       <c r="H21" s="3">
         <v>1248970.7199999983</v>
@@ -1514,8 +1519,8 @@
         <v>849384.05719999981</v>
       </c>
       <c r="M21" s="4"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="3"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
       <c r="Q21" s="5"/>
     </row>
     <row r="22" spans="1:17">
@@ -1535,10 +1540,10 @@
         <v>27</v>
       </c>
       <c r="F22" s="3">
-        <v>15048</v>
+        <v>15058</v>
       </c>
       <c r="G22" s="3">
-        <v>2398</v>
+        <v>2408</v>
       </c>
       <c r="H22" s="3">
         <v>867472.76000000047</v>
@@ -1556,8 +1561,8 @@
         <v>587725.51319999993</v>
       </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="3"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
       <c r="Q22" s="5"/>
     </row>
     <row r="23" spans="1:17">
@@ -1577,10 +1582,10 @@
         <v>28</v>
       </c>
       <c r="F23" s="3">
-        <v>17781</v>
+        <v>17791</v>
       </c>
       <c r="G23" s="3">
-        <v>2628</v>
+        <v>2638</v>
       </c>
       <c r="H23" s="3">
         <v>984094.76000000117</v>
@@ -1598,8 +1603,8 @@
         <v>667104.47999999963</v>
       </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="3"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
       <c r="Q23" s="5"/>
     </row>
     <row r="24" spans="1:17">
@@ -1619,10 +1624,10 @@
         <v>29</v>
       </c>
       <c r="F24" s="3">
-        <v>21881</v>
+        <v>21891</v>
       </c>
       <c r="G24" s="3">
-        <v>3248</v>
+        <v>3258</v>
       </c>
       <c r="H24" s="3">
         <v>1299403.3199999998</v>
@@ -1640,8 +1645,8 @@
         <v>873981.48480000033</v>
       </c>
       <c r="M24" s="4"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="3"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
       <c r="Q24" s="5"/>
     </row>
     <row r="25" spans="1:17">
@@ -1661,10 +1666,10 @@
         <v>19</v>
       </c>
       <c r="F25" s="3">
-        <v>26784</v>
+        <v>26794</v>
       </c>
       <c r="G25" s="3">
-        <v>1841</v>
+        <v>1851</v>
       </c>
       <c r="H25" s="3">
         <v>733246.8</v>
@@ -1682,8 +1687,8 @@
         <v>529778.59519999975</v>
       </c>
       <c r="M25" s="4"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="3"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
       <c r="Q25" s="5"/>
     </row>
     <row r="26" spans="1:17">
@@ -1703,10 +1708,10 @@
         <v>20</v>
       </c>
       <c r="F26" s="3">
-        <v>21459</v>
+        <v>21469</v>
       </c>
       <c r="G26" s="3">
-        <v>1684</v>
+        <v>1694</v>
       </c>
       <c r="H26" s="3">
         <v>709159.52</v>
@@ -1724,8 +1729,8 @@
         <v>520182.05759999994</v>
       </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="3"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
       <c r="Q26" s="5"/>
     </row>
     <row r="27" spans="1:17">
@@ -1745,10 +1750,10 @@
         <v>21</v>
       </c>
       <c r="F27" s="3">
-        <v>27521</v>
+        <v>27531</v>
       </c>
       <c r="G27" s="3">
-        <v>2248</v>
+        <v>2258</v>
       </c>
       <c r="H27" s="3">
         <v>892623</v>
@@ -1766,8 +1771,8 @@
         <v>629739.10999999975</v>
       </c>
       <c r="M27" s="4"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="3"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="31"/>
       <c r="Q27" s="5"/>
     </row>
     <row r="28" spans="1:17">
@@ -1787,10 +1792,10 @@
         <v>22</v>
       </c>
       <c r="F28" s="3">
-        <v>26664</v>
+        <v>26674</v>
       </c>
       <c r="G28" s="3">
-        <v>1898</v>
+        <v>1908</v>
       </c>
       <c r="H28" s="3">
         <v>772084.36000000034</v>
@@ -1808,8 +1813,8 @@
         <v>551346.40639999998</v>
       </c>
       <c r="M28" s="4"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="3"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
       <c r="Q28" s="5"/>
     </row>
     <row r="29" spans="1:17">
@@ -1829,10 +1834,10 @@
         <v>23</v>
       </c>
       <c r="F29" s="3">
-        <v>27071</v>
+        <v>27081</v>
       </c>
       <c r="G29" s="3">
-        <v>1837</v>
+        <v>1847</v>
       </c>
       <c r="H29" s="3">
         <v>825917.40000000026</v>
@@ -1850,8 +1855,8 @@
         <v>599371.57279999962</v>
       </c>
       <c r="M29" s="4"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="3"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
       <c r="Q29" s="5"/>
     </row>
     <row r="30" spans="1:17">
@@ -1871,10 +1876,10 @@
         <v>24</v>
       </c>
       <c r="F30" s="3">
-        <v>32286</v>
+        <v>32296</v>
       </c>
       <c r="G30" s="3">
-        <v>2269</v>
+        <v>2279</v>
       </c>
       <c r="H30" s="3">
         <v>942167.76000000047</v>
@@ -1892,8 +1897,8 @@
         <v>700759.64199999999</v>
       </c>
       <c r="M30" s="4"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="3"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
       <c r="Q30" s="5"/>
     </row>
     <row r="31" spans="1:17">
@@ -1913,10 +1918,10 @@
         <v>25</v>
       </c>
       <c r="F31" s="3">
-        <v>34771</v>
+        <v>34781</v>
       </c>
       <c r="G31" s="3">
-        <v>2443</v>
+        <v>2453</v>
       </c>
       <c r="H31" s="3">
         <v>930742.96</v>
@@ -1934,8 +1939,8 @@
         <v>653763.31679999968</v>
       </c>
       <c r="M31" s="4"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="3"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
       <c r="Q31" s="5"/>
     </row>
     <row r="32" spans="1:17">
@@ -1955,10 +1960,10 @@
         <v>26</v>
       </c>
       <c r="F32" s="3">
-        <v>31968</v>
+        <v>31978</v>
       </c>
       <c r="G32" s="3">
-        <v>2431</v>
+        <v>2441</v>
       </c>
       <c r="H32" s="3">
         <v>1082772.8000000003</v>
@@ -1976,8 +1981,8 @@
         <v>776512.89400000032</v>
       </c>
       <c r="M32" s="4"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="3"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
       <c r="Q32" s="5"/>
     </row>
     <row r="33" spans="1:17">
@@ -1997,10 +2002,10 @@
         <v>27</v>
       </c>
       <c r="F33" s="3">
-        <v>28827</v>
+        <v>28837</v>
       </c>
       <c r="G33" s="3">
-        <v>2384</v>
+        <v>2394</v>
       </c>
       <c r="H33" s="3">
         <v>1102336.6000000001</v>
@@ -2018,8 +2023,8 @@
         <v>793539.48559999967</v>
       </c>
       <c r="M33" s="4"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="3"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="31"/>
       <c r="Q33" s="5"/>
     </row>
     <row r="34" spans="1:17">
@@ -2039,10 +2044,10 @@
         <v>28</v>
       </c>
       <c r="F34" s="3">
-        <v>26781</v>
+        <v>26791</v>
       </c>
       <c r="G34" s="3">
-        <v>2148</v>
+        <v>2158</v>
       </c>
       <c r="H34" s="3">
         <v>1011115.2799999998</v>
@@ -2060,8 +2065,8 @@
         <v>730598.08320000011</v>
       </c>
       <c r="M34" s="4"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="3"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31"/>
       <c r="Q34" s="5"/>
     </row>
     <row r="35" spans="1:17">
@@ -2081,10 +2086,10 @@
         <v>29</v>
       </c>
       <c r="F35" s="3">
-        <v>35841</v>
+        <v>35851</v>
       </c>
       <c r="G35" s="3">
-        <v>2556</v>
+        <v>2566</v>
       </c>
       <c r="H35" s="3">
         <v>1120100.0799999996</v>
@@ -2102,8 +2107,8 @@
         <v>818211.86799999943</v>
       </c>
       <c r="M35" s="4"/>
-      <c r="N35" s="2"/>
-      <c r="O35" s="3"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
       <c r="Q35" s="5"/>
     </row>
     <row r="36" spans="1:17">
@@ -2123,10 +2128,10 @@
         <v>30</v>
       </c>
       <c r="F36" s="3">
-        <v>57724</v>
+        <v>57734</v>
       </c>
       <c r="G36" s="3">
-        <v>4791</v>
+        <v>4801</v>
       </c>
       <c r="H36" s="3">
         <v>1997792.7600000002</v>
@@ -2144,8 +2149,8 @@
         <v>1447902.6056000004</v>
       </c>
       <c r="M36" s="4"/>
-      <c r="N36" s="2"/>
-      <c r="O36" s="3"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="31"/>
       <c r="Q36" s="5"/>
     </row>
     <row r="37" spans="1:17">
@@ -2165,10 +2170,10 @@
         <v>19</v>
       </c>
       <c r="F37" s="3">
-        <v>25175</v>
+        <v>25185</v>
       </c>
       <c r="G37" s="3">
-        <v>1674</v>
+        <v>1684</v>
       </c>
       <c r="H37" s="3">
         <v>829587</v>
@@ -2186,8 +2191,8 @@
         <v>603346.7636000003</v>
       </c>
       <c r="M37" s="4"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="3"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
       <c r="Q37" s="5"/>
     </row>
     <row r="38" spans="1:17">
@@ -2207,10 +2212,10 @@
         <v>20</v>
       </c>
       <c r="F38" s="3">
-        <v>20511</v>
+        <v>20521</v>
       </c>
       <c r="G38" s="3">
-        <v>1739</v>
+        <v>1749</v>
       </c>
       <c r="H38" s="3">
         <v>853058.67999999993</v>
@@ -2228,8 +2233,8 @@
         <v>615651.60519999987</v>
       </c>
       <c r="M38" s="4"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="3"/>
+      <c r="N38" s="31"/>
+      <c r="O38" s="31"/>
       <c r="Q38" s="5"/>
     </row>
     <row r="39" spans="1:17">
@@ -2249,10 +2254,10 @@
         <v>21</v>
       </c>
       <c r="F39" s="3">
-        <v>22882</v>
+        <v>22892</v>
       </c>
       <c r="G39" s="3">
-        <v>2119</v>
+        <v>2129</v>
       </c>
       <c r="H39" s="3">
         <v>969360.20000000019</v>
@@ -2270,8 +2275,8 @@
         <v>714461.42039999994</v>
       </c>
       <c r="M39" s="4"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="3"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="31"/>
       <c r="Q39" s="5"/>
     </row>
     <row r="40" spans="1:17">
@@ -2291,10 +2296,10 @@
         <v>22</v>
       </c>
       <c r="F40" s="3">
-        <v>22609</v>
+        <v>22619</v>
       </c>
       <c r="G40" s="3">
-        <v>1832</v>
+        <v>1842</v>
       </c>
       <c r="H40" s="3">
         <v>901598.88000000047</v>
@@ -2312,8 +2317,8 @@
         <v>650104.63559999992</v>
       </c>
       <c r="M40" s="4"/>
-      <c r="N40" s="2"/>
-      <c r="O40" s="3"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
       <c r="Q40" s="5"/>
     </row>
     <row r="41" spans="1:17">
@@ -2333,10 +2338,10 @@
         <v>23</v>
       </c>
       <c r="F41" s="3">
-        <v>18728</v>
+        <v>18738</v>
       </c>
       <c r="G41" s="3">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="H41" s="3">
         <v>828317.23999999987</v>
@@ -2354,8 +2359,8 @@
         <v>595508.49319999968</v>
       </c>
       <c r="M41" s="4"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="3"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
       <c r="Q41" s="5"/>
     </row>
     <row r="42" spans="1:17">
@@ -2375,10 +2380,10 @@
         <v>24</v>
       </c>
       <c r="F42" s="3">
-        <v>22409</v>
+        <v>22419</v>
       </c>
       <c r="G42" s="3">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="H42" s="3">
         <v>822470.28000000014</v>
@@ -2396,8 +2401,8 @@
         <v>601459.20559999999</v>
       </c>
       <c r="M42" s="4"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="3"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
       <c r="Q42" s="5"/>
     </row>
     <row r="43" spans="1:17">
@@ -2417,10 +2422,10 @@
         <v>25</v>
       </c>
       <c r="F43" s="3">
-        <v>22949</v>
+        <v>22959</v>
       </c>
       <c r="G43" s="3">
-        <v>1893</v>
+        <v>1903</v>
       </c>
       <c r="H43" s="3">
         <v>844211.03999999992</v>
@@ -2438,8 +2443,8 @@
         <v>623573.89800000016</v>
       </c>
       <c r="M43" s="4"/>
-      <c r="N43" s="2"/>
-      <c r="O43" s="3"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
       <c r="Q43" s="5"/>
     </row>
     <row r="44" spans="1:17">
@@ -2459,10 +2464,10 @@
         <v>26</v>
       </c>
       <c r="F44" s="3">
-        <v>23100</v>
+        <v>23110</v>
       </c>
       <c r="G44" s="3">
-        <v>1991</v>
+        <v>2001</v>
       </c>
       <c r="H44" s="3">
         <v>866604.40000000026</v>
@@ -2480,8 +2485,8 @@
         <v>635422.96640000027</v>
       </c>
       <c r="M44" s="4"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="3"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
       <c r="Q44" s="5"/>
     </row>
     <row r="45" spans="1:17">
@@ -2501,10 +2506,10 @@
         <v>27</v>
       </c>
       <c r="F45" s="3">
-        <v>18215</v>
+        <v>18225</v>
       </c>
       <c r="G45" s="3">
-        <v>1647</v>
+        <v>1657</v>
       </c>
       <c r="H45" s="3">
         <v>781459.15999999992</v>
@@ -2522,8 +2527,8 @@
         <v>559652.76439999975</v>
       </c>
       <c r="M45" s="4"/>
-      <c r="N45" s="2"/>
-      <c r="O45" s="3"/>
+      <c r="N45" s="31"/>
+      <c r="O45" s="31"/>
       <c r="Q45" s="5"/>
     </row>
     <row r="46" spans="1:17">
@@ -2543,10 +2548,10 @@
         <v>28</v>
       </c>
       <c r="F46" s="3">
-        <v>19513</v>
+        <v>19523</v>
       </c>
       <c r="G46" s="3">
-        <v>1736</v>
+        <v>1746</v>
       </c>
       <c r="H46" s="3">
         <v>828727.35999999987</v>
@@ -2564,8 +2569,8 @@
         <v>598261.51320000004</v>
       </c>
       <c r="M46" s="4"/>
-      <c r="N46" s="2"/>
-      <c r="O46" s="3"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
       <c r="Q46" s="5"/>
     </row>
     <row r="47" spans="1:17">
@@ -2585,10 +2590,10 @@
         <v>29</v>
       </c>
       <c r="F47" s="3">
-        <v>26219</v>
+        <v>26229</v>
       </c>
       <c r="G47" s="3">
-        <v>1972</v>
+        <v>1982</v>
       </c>
       <c r="H47" s="3">
         <v>922886.71999999974</v>
@@ -2606,8 +2611,8 @@
         <v>665726.42399999953</v>
       </c>
       <c r="M47" s="4"/>
-      <c r="N47" s="2"/>
-      <c r="O47" s="3"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
       <c r="Q47" s="5"/>
     </row>
     <row r="48" spans="1:17">
@@ -2627,10 +2632,10 @@
         <v>19</v>
       </c>
       <c r="F48" s="3">
-        <v>10563</v>
+        <v>10573</v>
       </c>
       <c r="G48" s="3">
-        <v>2196</v>
+        <v>2206</v>
       </c>
       <c r="H48" s="3">
         <v>692225.76000000106</v>
@@ -2648,8 +2653,8 @@
         <v>276205.62799999979</v>
       </c>
       <c r="M48" s="4"/>
-      <c r="N48" s="2"/>
-      <c r="O48" s="3"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
       <c r="Q48" s="5"/>
     </row>
     <row r="49" spans="1:17">
@@ -2669,10 +2674,10 @@
         <v>20</v>
       </c>
       <c r="F49" s="3">
-        <v>9173</v>
+        <v>9183</v>
       </c>
       <c r="G49" s="3">
-        <v>2093</v>
+        <v>2103</v>
       </c>
       <c r="H49" s="3">
         <v>681397.72000000032</v>
@@ -2690,8 +2695,8 @@
         <v>271935.03199999989</v>
       </c>
       <c r="M49" s="4"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="3"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
       <c r="Q49" s="5"/>
     </row>
     <row r="50" spans="1:17">
@@ -2711,10 +2716,10 @@
         <v>21</v>
       </c>
       <c r="F50" s="3">
-        <v>10991</v>
+        <v>11001</v>
       </c>
       <c r="G50" s="3">
-        <v>2368</v>
+        <v>2378</v>
       </c>
       <c r="H50" s="3">
         <v>758287.04000000027</v>
@@ -2732,8 +2737,8 @@
         <v>306000.70880000002</v>
       </c>
       <c r="M50" s="4"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="3"/>
+      <c r="N50" s="31"/>
+      <c r="O50" s="31"/>
       <c r="Q50" s="5"/>
     </row>
     <row r="51" spans="1:17">
@@ -2753,10 +2758,10 @@
         <v>22</v>
       </c>
       <c r="F51" s="3">
-        <v>9539</v>
+        <v>9549</v>
       </c>
       <c r="G51" s="3">
-        <v>1947</v>
+        <v>1957</v>
       </c>
       <c r="H51" s="3">
         <v>550973.12000000058</v>
@@ -2774,8 +2779,8 @@
         <v>220935.00599999967</v>
       </c>
       <c r="M51" s="4"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="3"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="31"/>
       <c r="Q51" s="5"/>
     </row>
     <row r="52" spans="1:17">
@@ -2795,10 +2800,10 @@
         <v>23</v>
       </c>
       <c r="F52" s="3">
-        <v>9259</v>
+        <v>9269</v>
       </c>
       <c r="G52" s="3">
-        <v>2355</v>
+        <v>2365</v>
       </c>
       <c r="H52" s="3">
         <v>701317.84000000032</v>
@@ -2816,8 +2821,8 @@
         <v>280379.4271999998</v>
       </c>
       <c r="M52" s="4"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="3"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
       <c r="Q52" s="5"/>
     </row>
     <row r="53" spans="1:17">
@@ -2837,10 +2842,10 @@
         <v>24</v>
       </c>
       <c r="F53" s="3">
-        <v>11908</v>
+        <v>11918</v>
       </c>
       <c r="G53" s="3">
-        <v>3040</v>
+        <v>3050</v>
       </c>
       <c r="H53" s="3">
         <v>905403.59999999986</v>
@@ -2858,8 +2863,8 @@
         <v>356483.16680000012</v>
       </c>
       <c r="M53" s="4"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="3"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="31"/>
       <c r="Q53" s="5"/>
     </row>
     <row r="54" spans="1:17">
@@ -2879,10 +2884,10 @@
         <v>25</v>
       </c>
       <c r="F54" s="3">
-        <v>10836</v>
+        <v>10846</v>
       </c>
       <c r="G54" s="3">
-        <v>2732</v>
+        <v>2742</v>
       </c>
       <c r="H54" s="3">
         <v>869330.96000000043</v>
@@ -2900,8 +2905,8 @@
         <v>348590.24160000001</v>
       </c>
       <c r="M54" s="4"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="3"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
       <c r="Q54" s="5"/>
     </row>
     <row r="55" spans="1:17">
@@ -2921,10 +2926,10 @@
         <v>26</v>
       </c>
       <c r="F55" s="3">
-        <v>12143</v>
+        <v>12153</v>
       </c>
       <c r="G55" s="3">
-        <v>2736</v>
+        <v>2746</v>
       </c>
       <c r="H55" s="3">
         <v>855369.24000000057</v>
@@ -2942,8 +2947,8 @@
         <v>341542.61719999992</v>
       </c>
       <c r="M55" s="4"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="3"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
       <c r="Q55" s="5"/>
     </row>
     <row r="56" spans="1:17">
@@ -2963,10 +2968,10 @@
         <v>27</v>
       </c>
       <c r="F56" s="3">
-        <v>10821</v>
+        <v>10831</v>
       </c>
       <c r="G56" s="3">
-        <v>2678</v>
+        <v>2688</v>
       </c>
       <c r="H56" s="3">
         <v>842053.23999999883</v>
@@ -2984,8 +2989,8 @@
         <v>339458.98399999971</v>
       </c>
       <c r="M56" s="4"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="3"/>
+      <c r="N56" s="31"/>
+      <c r="O56" s="31"/>
       <c r="Q56" s="5"/>
     </row>
     <row r="57" spans="1:17">
@@ -3005,10 +3010,10 @@
         <v>28</v>
       </c>
       <c r="F57" s="3">
-        <v>9784</v>
+        <v>9794</v>
       </c>
       <c r="G57" s="3">
-        <v>2466</v>
+        <v>2476</v>
       </c>
       <c r="H57" s="3">
         <v>719011.00000000012</v>
@@ -3026,8 +3031,8 @@
         <v>286865.98559999984</v>
       </c>
       <c r="M57" s="4"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="3"/>
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
       <c r="Q57" s="5"/>
     </row>
     <row r="58" spans="1:17">
@@ -3047,10 +3052,10 @@
         <v>29</v>
       </c>
       <c r="F58" s="3">
-        <v>12987</v>
+        <v>12997</v>
       </c>
       <c r="G58" s="3">
-        <v>3198</v>
+        <v>3208</v>
       </c>
       <c r="H58" s="3">
         <v>943352.03999999922</v>
@@ -3068,8 +3073,8 @@
         <v>380392.19639999996</v>
       </c>
       <c r="M58" s="4"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="3"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
       <c r="Q58" s="5"/>
     </row>
     <row r="59" spans="1:17">
@@ -3089,10 +3094,10 @@
         <v>30</v>
       </c>
       <c r="F59" s="3">
-        <v>24722</v>
+        <v>24732</v>
       </c>
       <c r="G59" s="3">
-        <v>6300</v>
+        <v>6310</v>
       </c>
       <c r="H59" s="3">
         <v>1686194.4799999958</v>
@@ -3110,8 +3115,8 @@
         <v>678901.70319999987</v>
       </c>
       <c r="M59" s="4"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="3"/>
+      <c r="N59" s="31"/>
+      <c r="O59" s="31"/>
       <c r="Q59" s="5"/>
     </row>
     <row r="60" spans="1:17">
@@ -3131,10 +3136,10 @@
         <v>19</v>
       </c>
       <c r="F60" s="3">
-        <v>12275</v>
+        <v>12285</v>
       </c>
       <c r="G60" s="3">
-        <v>2607</v>
+        <v>2617</v>
       </c>
       <c r="H60" s="3">
         <v>797988.44000000029</v>
@@ -3152,8 +3157,8 @@
         <v>320104.39960000006</v>
       </c>
       <c r="M60" s="4"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="3"/>
+      <c r="N60" s="31"/>
+      <c r="O60" s="31"/>
       <c r="Q60" s="5"/>
     </row>
     <row r="61" spans="1:17">
@@ -3173,10 +3178,10 @@
         <v>20</v>
       </c>
       <c r="F61" s="3">
-        <v>9959</v>
+        <v>9969</v>
       </c>
       <c r="G61" s="3">
-        <v>2502</v>
+        <v>2512</v>
       </c>
       <c r="H61" s="3">
         <v>710316.40000000061</v>
@@ -3194,8 +3199,8 @@
         <v>285012.8272</v>
       </c>
       <c r="M61" s="4"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="3"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
       <c r="Q61" s="5"/>
     </row>
     <row r="62" spans="1:17">
@@ -3215,10 +3220,10 @@
         <v>21</v>
       </c>
       <c r="F62" s="3">
-        <v>10972</v>
+        <v>10982</v>
       </c>
       <c r="G62" s="3">
-        <v>2954</v>
+        <v>2964</v>
       </c>
       <c r="H62" s="3">
         <v>785422.68000000098</v>
@@ -3236,8 +3241,8 @@
         <v>314161.39160000003</v>
       </c>
       <c r="M62" s="4"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="3"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
       <c r="Q62" s="5"/>
     </row>
     <row r="63" spans="1:17">
@@ -3257,10 +3262,10 @@
         <v>22</v>
       </c>
       <c r="F63" s="3">
-        <v>9970</v>
+        <v>9980</v>
       </c>
       <c r="G63" s="3">
-        <v>2261</v>
+        <v>2271</v>
       </c>
       <c r="H63" s="3">
         <v>663021.55999999994</v>
@@ -3278,8 +3283,8 @@
         <v>266198.9515999998</v>
       </c>
       <c r="M63" s="4"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="3"/>
+      <c r="N63" s="31"/>
+      <c r="O63" s="31"/>
       <c r="Q63" s="5"/>
     </row>
     <row r="64" spans="1:17">
@@ -3299,10 +3304,10 @@
         <v>23</v>
       </c>
       <c r="F64" s="3">
-        <v>9440</v>
+        <v>9450</v>
       </c>
       <c r="G64" s="3">
-        <v>2359</v>
+        <v>2369</v>
       </c>
       <c r="H64" s="3">
         <v>746786.72000000114</v>
@@ -3320,8 +3325,8 @@
         <v>294983.28279999993</v>
       </c>
       <c r="M64" s="4"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="3"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
       <c r="Q64" s="5"/>
     </row>
     <row r="65" spans="1:17">
@@ -3341,10 +3346,10 @@
         <v>24</v>
       </c>
       <c r="F65" s="3">
-        <v>11580</v>
+        <v>11590</v>
       </c>
       <c r="G65" s="3">
-        <v>3200</v>
+        <v>3210</v>
       </c>
       <c r="H65" s="3">
         <v>917265.92000000039</v>
@@ -3362,8 +3367,8 @@
         <v>364592.42079999927</v>
       </c>
       <c r="M65" s="4"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="3"/>
+      <c r="N65" s="31"/>
+      <c r="O65" s="31"/>
       <c r="Q65" s="5"/>
     </row>
     <row r="66" spans="1:17">
@@ -3383,10 +3388,10 @@
         <v>25</v>
       </c>
       <c r="F66" s="3">
-        <v>11444</v>
+        <v>11454</v>
       </c>
       <c r="G66" s="3">
-        <v>2958</v>
+        <v>2968</v>
       </c>
       <c r="H66" s="3">
         <v>865181.80000000016</v>
@@ -3404,8 +3409,8 @@
         <v>344045.78359999968</v>
       </c>
       <c r="M66" s="4"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="3"/>
+      <c r="N66" s="31"/>
+      <c r="O66" s="31"/>
       <c r="Q66" s="5"/>
     </row>
     <row r="67" spans="1:17">
@@ -3425,10 +3430,10 @@
         <v>26</v>
       </c>
       <c r="F67" s="3">
-        <v>14277</v>
+        <v>14287</v>
       </c>
       <c r="G67" s="3">
-        <v>4184</v>
+        <v>4194</v>
       </c>
       <c r="H67" s="3">
         <v>1074431.8400000001</v>
@@ -3446,8 +3451,8 @@
         <v>426838.52640000009</v>
       </c>
       <c r="M67" s="4"/>
-      <c r="N67" s="2"/>
-      <c r="O67" s="3"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
       <c r="Q67" s="5"/>
     </row>
     <row r="68" spans="1:17">
@@ -3467,10 +3472,10 @@
         <v>27</v>
       </c>
       <c r="F68" s="3">
-        <v>11197</v>
+        <v>11207</v>
       </c>
       <c r="G68" s="3">
-        <v>2921</v>
+        <v>2931</v>
       </c>
       <c r="H68" s="3">
         <v>732642.20000000065</v>
@@ -3488,8 +3493,8 @@
         <v>291404.304</v>
       </c>
       <c r="M68" s="4"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="3"/>
+      <c r="N68" s="31"/>
+      <c r="O68" s="31"/>
       <c r="Q68" s="5"/>
     </row>
     <row r="69" spans="1:17">
@@ -3509,10 +3514,10 @@
         <v>28</v>
       </c>
       <c r="F69" s="3">
-        <v>11877</v>
+        <v>11887</v>
       </c>
       <c r="G69" s="3">
-        <v>2903</v>
+        <v>2913</v>
       </c>
       <c r="H69" s="3">
         <v>794110.56000000017</v>
@@ -3530,8 +3535,8 @@
         <v>315991.37279999955</v>
       </c>
       <c r="M69" s="4"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="3"/>
+      <c r="N69" s="31"/>
+      <c r="O69" s="31"/>
       <c r="Q69" s="5"/>
     </row>
     <row r="70" spans="1:17">
@@ -3551,10 +3556,10 @@
         <v>29</v>
       </c>
       <c r="F70" s="3">
-        <v>13301</v>
+        <v>13311</v>
       </c>
       <c r="G70" s="3">
-        <v>3347</v>
+        <v>3357</v>
       </c>
       <c r="H70" s="3">
         <v>1035427.9599999994</v>
@@ -3572,8 +3577,8 @@
         <v>410594.34519999992</v>
       </c>
       <c r="M70" s="4"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="3"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
       <c r="Q70" s="5"/>
     </row>
     <row r="71" spans="1:17">
@@ -3593,10 +3598,10 @@
         <v>30</v>
       </c>
       <c r="F71" s="3">
-        <v>22533</v>
+        <v>22543</v>
       </c>
       <c r="G71" s="3">
-        <v>5154</v>
+        <v>5164</v>
       </c>
       <c r="H71" s="3">
         <v>1869814.12</v>
@@ -3614,8 +3619,8 @@
         <v>1291576.8811999995</v>
       </c>
       <c r="M71" s="4"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="3"/>
+      <c r="N71" s="31"/>
+      <c r="O71" s="31"/>
       <c r="Q71" s="5"/>
     </row>
     <row r="72" spans="1:17">
@@ -3635,10 +3640,10 @@
         <v>30</v>
       </c>
       <c r="F72" s="3">
-        <v>23197</v>
+        <v>23207</v>
       </c>
       <c r="G72" s="3">
-        <v>6270</v>
+        <v>6280</v>
       </c>
       <c r="H72" s="3">
         <v>1768116.4799999953</v>
@@ -3656,8 +3661,8 @@
         <v>712151.37759999943</v>
       </c>
       <c r="M72" s="4"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="3"/>
+      <c r="N72" s="31"/>
+      <c r="O72" s="31"/>
       <c r="Q72" s="5"/>
     </row>
     <row r="73" spans="1:17">
@@ -3677,10 +3682,10 @@
         <v>30</v>
       </c>
       <c r="F73" s="3">
-        <v>41075</v>
+        <v>41085</v>
       </c>
       <c r="G73" s="3">
-        <v>4178</v>
+        <v>4188</v>
       </c>
       <c r="H73" s="3">
         <v>1681034.9599999997</v>
@@ -3698,8 +3703,8 @@
         <v>1229942.2535999999</v>
       </c>
       <c r="M73" s="4"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="3"/>
+      <c r="N73" s="31"/>
+      <c r="O73" s="31"/>
       <c r="Q73" s="5"/>
     </row>
   </sheetData>
@@ -4040,51 +4045,51 @@
       </c>
       <c r="C9" s="18">
         <f>IFERROR(SUMIFS(RET_KPI_Sales_Database!$F:$F,RET_KPI_Sales_Database!$C:$C,C$3,RET_KPI_Sales_Database!$D:$D,C$4),0)</f>
-        <v>229779</v>
+        <v>229899</v>
       </c>
       <c r="D9" s="18">
         <f>IFERROR(SUMIFS(RET_KPI_Sales_Database!$F:$F,RET_KPI_Sales_Database!$C:$C,D$3,RET_KPI_Sales_Database!$D:$D,D$4),0)</f>
-        <v>267616</v>
+        <v>267736</v>
       </c>
       <c r="E9" s="19">
         <f>(C9-D9)/D9</f>
-        <v>-0.14138541791223244</v>
+        <v>-0.14132204858517344</v>
       </c>
       <c r="F9" s="18">
         <f>IFERROR(SUMIFS(RET_KPI_Sales_Database!$F:$F,RET_KPI_Sales_Database!$C:$C,F$3,RET_KPI_Sales_Database!$D:$D,F$4),0)</f>
-        <v>283385</v>
+        <v>283505</v>
       </c>
       <c r="G9" s="18">
         <f>IFERROR(SUMIFS(RET_KPI_Sales_Database!$F:$F,RET_KPI_Sales_Database!$C:$C,G$3,RET_KPI_Sales_Database!$D:$D,G$4),0)</f>
-        <v>377697</v>
+        <v>377817</v>
       </c>
       <c r="H9" s="19">
         <f>IFERROR((F9-G9)/G9," ")</f>
-        <v>-0.24970280409958248</v>
+        <v>-0.24962349497243375</v>
       </c>
       <c r="I9" s="18">
         <f>IFERROR(SUMIFS(RET_KPI_Sales_Database!$F:$F,RET_KPI_Sales_Database!$C:$C,I$3,RET_KPI_Sales_Database!$D:$D,I$4),0)</f>
-        <v>149489</v>
+        <v>149609</v>
       </c>
       <c r="J9" s="18">
         <f>IFERROR(SUMIFS(RET_KPI_Sales_Database!$F:$F,RET_KPI_Sales_Database!$C:$C,J$3,RET_KPI_Sales_Database!$D:$D,J$4),0)</f>
-        <v>142726</v>
+        <v>142846</v>
       </c>
       <c r="K9" s="19">
         <f>(I9-J9)/J9</f>
-        <v>4.7384498970054513E-2</v>
+        <v>4.7344692886045113E-2</v>
       </c>
       <c r="L9" s="18">
         <f>C9+F9+I9</f>
-        <v>662653</v>
+        <v>663013</v>
       </c>
       <c r="M9" s="30">
         <f>D9+G9+J9</f>
-        <v>788039</v>
+        <v>788399</v>
       </c>
       <c r="N9" s="19">
         <f>(L9-M9)/M9</f>
-        <v>-0.1591114145365902</v>
+        <v>-0.1590387608304932</v>
       </c>
       <c r="Q9" s="20"/>
     </row>
@@ -4094,51 +4099,51 @@
       </c>
       <c r="C10" s="18">
         <f>SUMIFS(RET_KPI_Sales_Database!$G:$G,RET_KPI_Sales_Database!$C:$C,C$3,RET_KPI_Sales_Database!$D:$D,C$4)</f>
-        <v>34235</v>
+        <v>34355</v>
       </c>
       <c r="D10" s="18">
         <f>SUMIFS(RET_KPI_Sales_Database!$G:$G,RET_KPI_Sales_Database!$C:$C,D$3,RET_KPI_Sales_Database!$D:$D,D$4)</f>
-        <v>33451</v>
+        <v>33571</v>
       </c>
       <c r="E10" s="21">
         <f>(C10-D10)/D10</f>
-        <v>2.3437266449433499E-2</v>
+        <v>2.3353489619016413E-2</v>
       </c>
       <c r="F10" s="18">
         <f>SUMIFS(RET_KPI_Sales_Database!$G:$G,RET_KPI_Sales_Database!$C:$C,F$3,RET_KPI_Sales_Database!$D:$D,F$4)</f>
-        <v>24075</v>
+        <v>24195</v>
       </c>
       <c r="G10" s="18">
         <f>SUMIFS(RET_KPI_Sales_Database!$G:$G,RET_KPI_Sales_Database!$C:$C,G$3,RET_KPI_Sales_Database!$D:$D,G$4)</f>
-        <v>28530</v>
+        <v>28650</v>
       </c>
       <c r="H10" s="21">
         <f>IFERROR((F10-G10)/G10," ")</f>
-        <v>-0.15615141955835962</v>
+        <v>-0.15549738219895287</v>
       </c>
       <c r="I10" s="18">
         <f>SUMIFS(RET_KPI_Sales_Database!$G:$G,RET_KPI_Sales_Database!$C:$C,I$3,RET_KPI_Sales_Database!$D:$D,I$4)</f>
-        <v>38466</v>
+        <v>38586</v>
       </c>
       <c r="J10" s="18">
         <f>SUMIFS(RET_KPI_Sales_Database!$G:$G,RET_KPI_Sales_Database!$C:$C,J$3,RET_KPI_Sales_Database!$D:$D,J$4)</f>
-        <v>34109</v>
+        <v>34229</v>
       </c>
       <c r="K10" s="21">
         <f>(I10-J10)/J10</f>
-        <v>0.12773754727491277</v>
+        <v>0.12728972508691461</v>
       </c>
       <c r="L10" s="18">
         <f>C10+F10+I10</f>
-        <v>96776</v>
+        <v>97136</v>
       </c>
       <c r="M10" s="22">
         <f>D10+G10+J10</f>
-        <v>96090</v>
+        <v>96450</v>
       </c>
       <c r="N10" s="21">
         <f>(L10-M10)/M10</f>
-        <v>7.1391403892184409E-3</v>
+        <v>7.1124935199585277E-3</v>
       </c>
       <c r="Q10" s="20"/>
     </row>
@@ -4148,51 +4153,51 @@
       </c>
       <c r="C11" s="23">
         <f>IFERROR(C10/C9,0)</f>
-        <v>0.14899098699184868</v>
+        <v>0.14943518675592327</v>
       </c>
       <c r="D11" s="24">
         <f>IFERROR(D10/D9,0)</f>
-        <v>0.12499626330264259</v>
+        <v>0.12538844234619176</v>
       </c>
       <c r="E11" s="25">
         <f>(C11-D11)*100</f>
-        <v>2.399472368920609</v>
+        <v>2.4046744409731509</v>
       </c>
       <c r="F11" s="23">
         <f>IFERROR(F10/F9,0)</f>
-        <v>8.4955096423593349E-2</v>
+        <v>8.5342410186769191E-2</v>
       </c>
       <c r="G11" s="23">
         <f>IFERROR(G10/G9,0)</f>
-        <v>7.5536739767591482E-2</v>
+        <v>7.583036231826519E-2</v>
       </c>
       <c r="H11" s="25">
         <f>(F11-G11)*100</f>
-        <v>0.94183566560018672</v>
+        <v>0.95120478685040011</v>
       </c>
       <c r="I11" s="23">
         <f>IFERROR(I10/I9,0)</f>
-        <v>0.25731659185625699</v>
+        <v>0.25791229137284521</v>
       </c>
       <c r="J11" s="23">
         <f>IFERROR(J10/J9,0)</f>
-        <v>0.23898238583019213</v>
+        <v>0.23962169049185836</v>
       </c>
       <c r="K11" s="25">
         <f>(I11-J11)*100</f>
-        <v>1.8334206026064863</v>
+        <v>1.8290600880986858</v>
       </c>
       <c r="L11" s="24">
         <f>L10/L9</f>
-        <v>0.14604325340713767</v>
+        <v>0.14650693123664241</v>
       </c>
       <c r="M11" s="24">
         <f>M10/M9</f>
-        <v>0.12193558948224643</v>
+        <v>0.12233653264400386</v>
       </c>
       <c r="N11" s="25">
         <f>(L11-M11)*100</f>
-        <v>2.4107663924891236</v>
+        <v>2.4170398592638547</v>
       </c>
       <c r="Q11" s="20"/>
     </row>
@@ -4202,51 +4207,51 @@
       </c>
       <c r="C12" s="26">
         <f>IFERROR(C5/C10,0)</f>
-        <v>380.52471681028197</v>
+        <v>379.19556629311609</v>
       </c>
       <c r="D12" s="26">
         <f>IFERROR(D5/D10,0)</f>
-        <v>382.71963767899325</v>
+        <v>381.35160108426925</v>
       </c>
       <c r="E12" s="21">
         <f>(C12-D12)/D12</f>
-        <v>-5.7350620470441403E-3</v>
+        <v>-5.6536665508236071E-3</v>
       </c>
       <c r="F12" s="26">
         <f>IFERROR(F5/F10,0)</f>
-        <v>462.27688141225337</v>
+        <v>459.98412564579456</v>
       </c>
       <c r="G12" s="26">
         <f>IFERROR(G5/G10,0)</f>
-        <v>424.8180623904662</v>
+        <v>423.03871972076792</v>
       </c>
       <c r="H12" s="21">
         <f>IFERROR((F12-G12)/G12," ")</f>
-        <v>8.8176144891309663E-2</v>
+        <v>8.7333391017760581E-2</v>
       </c>
       <c r="I12" s="26">
         <f>IFERROR(I5/I10,0)</f>
-        <v>283.12568398065821</v>
+        <v>282.24518115378629</v>
       </c>
       <c r="J12" s="26">
         <f>IFERROR(J5/J10,0)</f>
-        <v>299.18543610190846</v>
+        <v>298.13655204651013</v>
       </c>
       <c r="K12" s="21">
         <f>(I12-J12)/J12</f>
-        <v>-5.367825496619423E-2</v>
+        <v>-5.3302323326811479E-2</v>
       </c>
       <c r="L12" s="26">
         <f>L5/L10</f>
-        <v>362.14859221294535</v>
+        <v>360.80641739416899</v>
       </c>
       <c r="M12" s="26">
         <f>M5/M10</f>
-        <v>365.56696805078565</v>
+        <v>364.20248792120265</v>
       </c>
       <c r="N12" s="21">
         <f>(L12-M12)/M12</f>
-        <v>-9.3508881726026474E-3</v>
+        <v>-9.3246769027245571E-3</v>
       </c>
       <c r="Q12" s="20"/>
     </row>
@@ -4256,51 +4261,51 @@
       </c>
       <c r="C13" s="27">
         <f>IFERROR(C6/C10,0)</f>
-        <v>2.6140207390097854</v>
+        <v>2.6048901178867703</v>
       </c>
       <c r="D13" s="27">
         <f>IFERROR(D6/D10,0)</f>
-        <v>2.5573525455143344</v>
+        <v>2.5482112537606865</v>
       </c>
       <c r="E13" s="28">
         <f>C13-D13</f>
-        <v>5.6668193495450936E-2</v>
+        <v>5.6678864126083806E-2</v>
       </c>
       <c r="F13" s="27">
         <f>IFERROR(F6/F10,0)</f>
-        <v>2.3406438213914851</v>
+        <v>2.3290349245711925</v>
       </c>
       <c r="G13" s="27">
         <f>IFERROR(G6/G10,0)</f>
-        <v>2.112758499824746</v>
+        <v>2.1039092495636997</v>
       </c>
       <c r="H13" s="28">
         <f>F13-G13</f>
-        <v>0.22788532156673913</v>
+        <v>0.22512567500749281</v>
       </c>
       <c r="I13" s="27">
         <f>IFERROR(I6/I10,0)</f>
-        <v>3.703790360318203</v>
+        <v>3.6922718084279271</v>
       </c>
       <c r="J13" s="27">
         <f>IFERROR(J6/J10,0)</f>
-        <v>3.7961241900964553</v>
+        <v>3.7828157410383008</v>
       </c>
       <c r="K13" s="28">
         <f>I13-J13</f>
-        <v>-9.233382977825233E-2</v>
+        <v>-9.0543932610373634E-2</v>
       </c>
       <c r="L13" s="27">
         <f>L6/L10</f>
-        <v>2.9791683888567415</v>
+        <v>2.968127161917312</v>
       </c>
       <c r="M13" s="23">
         <f>M6/M10</f>
-        <v>2.8650744094078466</v>
+        <v>2.8543805080352516</v>
       </c>
       <c r="N13" s="28">
         <f>L13-M13</f>
-        <v>0.11409397944889488</v>
+        <v>0.1137466538820604</v>
       </c>
       <c r="Q13" s="20"/>
     </row>

--- a/RET_KPI_Sales_Database.xlsx
+++ b/RET_KPI_Sales_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/30722571119c7a42/Documents/Fede/AI Test/Retail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{013E9734-E5F4-485C-9734-B8A02A00E18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0811452-6F43-4E88-97E3-1F301BD90DD6}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{013E9734-E5F4-485C-9734-B8A02A00E18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{165BEE14-5933-4DC5-81CF-A27EA00B348F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Dashboard!$O$3:$AI$8952</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RET_KPI_Sales_Database!$A$1:$K$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RET_KPI_Sales_Database!$A$1:$K$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="37">
   <si>
     <t>Panama</t>
   </si>
@@ -627,7 +627,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{405DFD03-4F9B-482B-9B5A-511F39FADA19}">
-  <dimension ref="A1:Q73"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Q109"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
@@ -1187,7 +1188,7 @@
       <c r="O13" s="31"/>
       <c r="Q13" s="5"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" hidden="1">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1229,7 +1230,7 @@
       <c r="O14" s="31"/>
       <c r="Q14" s="5"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" hidden="1">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1272,7 @@
       <c r="O15" s="31"/>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" hidden="1">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1314,7 @@
       <c r="O16" s="31"/>
       <c r="Q16" s="5"/>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" hidden="1">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -1355,7 +1356,7 @@
       <c r="O17" s="31"/>
       <c r="Q17" s="5"/>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" hidden="1">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -1397,7 +1398,7 @@
       <c r="O18" s="31"/>
       <c r="Q18" s="5"/>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" hidden="1">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +1440,7 @@
       <c r="O19" s="31"/>
       <c r="Q19" s="5"/>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" hidden="1">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -1481,7 +1482,7 @@
       <c r="O20" s="31"/>
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" hidden="1">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1524,7 @@
       <c r="O21" s="31"/>
       <c r="Q21" s="5"/>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" hidden="1">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1566,7 @@
       <c r="O22" s="31"/>
       <c r="Q22" s="5"/>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" hidden="1">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1608,7 @@
       <c r="O23" s="31"/>
       <c r="Q23" s="5"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" hidden="1">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -2153,7 +2154,7 @@
       <c r="O36" s="31"/>
       <c r="Q36" s="5"/>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" hidden="1">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -2195,7 +2196,7 @@
       <c r="O37" s="31"/>
       <c r="Q37" s="5"/>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:17" hidden="1">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -2237,7 +2238,7 @@
       <c r="O38" s="31"/>
       <c r="Q38" s="5"/>
     </row>
-    <row r="39" spans="1:17">
+    <row r="39" spans="1:17" hidden="1">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -2279,7 +2280,7 @@
       <c r="O39" s="31"/>
       <c r="Q39" s="5"/>
     </row>
-    <row r="40" spans="1:17">
+    <row r="40" spans="1:17" hidden="1">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2322,7 @@
       <c r="O40" s="31"/>
       <c r="Q40" s="5"/>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:17" hidden="1">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -2363,7 +2364,7 @@
       <c r="O41" s="31"/>
       <c r="Q41" s="5"/>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:17" hidden="1">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -2405,7 +2406,7 @@
       <c r="O42" s="31"/>
       <c r="Q42" s="5"/>
     </row>
-    <row r="43" spans="1:17">
+    <row r="43" spans="1:17" hidden="1">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -2447,7 +2448,7 @@
       <c r="O43" s="31"/>
       <c r="Q43" s="5"/>
     </row>
-    <row r="44" spans="1:17">
+    <row r="44" spans="1:17" hidden="1">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -2489,7 +2490,7 @@
       <c r="O44" s="31"/>
       <c r="Q44" s="5"/>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" hidden="1">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -2531,7 +2532,7 @@
       <c r="O45" s="31"/>
       <c r="Q45" s="5"/>
     </row>
-    <row r="46" spans="1:17">
+    <row r="46" spans="1:17" hidden="1">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -2573,7 +2574,7 @@
       <c r="O46" s="31"/>
       <c r="Q46" s="5"/>
     </row>
-    <row r="47" spans="1:17">
+    <row r="47" spans="1:17" hidden="1">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -3119,7 +3120,7 @@
       <c r="O59" s="31"/>
       <c r="Q59" s="5"/>
     </row>
-    <row r="60" spans="1:17">
+    <row r="60" spans="1:17" hidden="1">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -3161,7 +3162,7 @@
       <c r="O60" s="31"/>
       <c r="Q60" s="5"/>
     </row>
-    <row r="61" spans="1:17">
+    <row r="61" spans="1:17" hidden="1">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -3203,7 +3204,7 @@
       <c r="O61" s="31"/>
       <c r="Q61" s="5"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" hidden="1">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -3245,7 +3246,7 @@
       <c r="O62" s="31"/>
       <c r="Q62" s="5"/>
     </row>
-    <row r="63" spans="1:17">
+    <row r="63" spans="1:17" hidden="1">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -3287,7 +3288,7 @@
       <c r="O63" s="31"/>
       <c r="Q63" s="5"/>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" hidden="1">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -3329,7 +3330,7 @@
       <c r="O64" s="31"/>
       <c r="Q64" s="5"/>
     </row>
-    <row r="65" spans="1:17">
+    <row r="65" spans="1:17" hidden="1">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -3371,7 +3372,7 @@
       <c r="O65" s="31"/>
       <c r="Q65" s="5"/>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" hidden="1">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -3413,7 +3414,7 @@
       <c r="O66" s="31"/>
       <c r="Q66" s="5"/>
     </row>
-    <row r="67" spans="1:17">
+    <row r="67" spans="1:17" hidden="1">
       <c r="A67" t="s">
         <v>0</v>
       </c>
@@ -3455,7 +3456,7 @@
       <c r="O67" s="31"/>
       <c r="Q67" s="5"/>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" hidden="1">
       <c r="A68" t="s">
         <v>0</v>
       </c>
@@ -3497,7 +3498,7 @@
       <c r="O68" s="31"/>
       <c r="Q68" s="5"/>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:17" hidden="1">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -3539,7 +3540,7 @@
       <c r="O69" s="31"/>
       <c r="Q69" s="5"/>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" hidden="1">
       <c r="A70" t="s">
         <v>0</v>
       </c>
@@ -3581,7 +3582,7 @@
       <c r="O70" s="31"/>
       <c r="Q70" s="5"/>
     </row>
-    <row r="71" spans="1:17">
+    <row r="71" spans="1:17" hidden="1">
       <c r="A71" t="s">
         <v>0</v>
       </c>
@@ -3623,7 +3624,7 @@
       <c r="O71" s="31"/>
       <c r="Q71" s="5"/>
     </row>
-    <row r="72" spans="1:17">
+    <row r="72" spans="1:17" hidden="1">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -3665,7 +3666,7 @@
       <c r="O72" s="31"/>
       <c r="Q72" s="5"/>
     </row>
-    <row r="73" spans="1:17">
+    <row r="73" spans="1:17" hidden="1">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -3707,8 +3708,1382 @@
       <c r="O73" s="31"/>
       <c r="Q73" s="5"/>
     </row>
+    <row r="74" spans="1:17">
+      <c r="A74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74">
+        <v>2023</v>
+      </c>
+      <c r="E74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" s="3">
+        <v>24121</v>
+      </c>
+      <c r="G74" s="3">
+        <v>2460</v>
+      </c>
+      <c r="H74" s="3">
+        <v>828809.64000000048</v>
+      </c>
+      <c r="I74" s="3">
+        <v>240717.38173224201</v>
+      </c>
+      <c r="J74" s="3">
+        <v>5078</v>
+      </c>
+      <c r="K74" s="3">
+        <v>1573</v>
+      </c>
+      <c r="L74" s="6">
+        <v>565074.35880000005</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17">
+      <c r="A75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75">
+        <v>2023</v>
+      </c>
+      <c r="E75" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" s="3">
+        <v>18740</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1906</v>
+      </c>
+      <c r="H75" s="3">
+        <v>753842.96000000078</v>
+      </c>
+      <c r="I75" s="3">
+        <v>476334.86135537142</v>
+      </c>
+      <c r="J75" s="3">
+        <v>4201</v>
+      </c>
+      <c r="K75" s="3">
+        <v>2297</v>
+      </c>
+      <c r="L75" s="6">
+        <v>506628.81800000014</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17">
+      <c r="A76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76">
+        <v>2023</v>
+      </c>
+      <c r="E76" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" s="3">
+        <v>19475</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2439</v>
+      </c>
+      <c r="H76" s="3">
+        <v>1021389.2400000007</v>
+      </c>
+      <c r="I76" s="3">
+        <v>862471.05727020523</v>
+      </c>
+      <c r="J76" s="3">
+        <v>5291</v>
+      </c>
+      <c r="K76" s="3">
+        <v>4091</v>
+      </c>
+      <c r="L76" s="6">
+        <v>676586.9432000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17">
+      <c r="A77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77">
+        <v>2023</v>
+      </c>
+      <c r="E77" t="s">
+        <v>22</v>
+      </c>
+      <c r="F77" s="3">
+        <v>18268</v>
+      </c>
+      <c r="G77" s="3">
+        <v>2370</v>
+      </c>
+      <c r="H77" s="3">
+        <v>921424.72000000009</v>
+      </c>
+      <c r="I77" s="3">
+        <v>638061.60644272016</v>
+      </c>
+      <c r="J77" s="3">
+        <v>5313</v>
+      </c>
+      <c r="K77" s="3">
+        <v>3274</v>
+      </c>
+      <c r="L77" s="6">
+        <v>625224.59199999948</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17">
+      <c r="A78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78">
+        <v>2023</v>
+      </c>
+      <c r="E78" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78" s="3">
+        <v>17785</v>
+      </c>
+      <c r="G78" s="3">
+        <v>2235</v>
+      </c>
+      <c r="H78" s="3">
+        <v>887137.200000001</v>
+      </c>
+      <c r="I78" s="3">
+        <v>699973.31037813635</v>
+      </c>
+      <c r="J78" s="3">
+        <v>4434</v>
+      </c>
+      <c r="K78" s="3">
+        <v>3308</v>
+      </c>
+      <c r="L78" s="6">
+        <v>603991.19759999972</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17">
+      <c r="A79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79">
+        <v>2023</v>
+      </c>
+      <c r="E79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="3">
+        <v>25983</v>
+      </c>
+      <c r="G79" s="3">
+        <v>3264</v>
+      </c>
+      <c r="H79" s="3">
+        <v>1312448.2399999998</v>
+      </c>
+      <c r="I79" s="3">
+        <v>1028462.8384033352</v>
+      </c>
+      <c r="J79" s="3">
+        <v>7019</v>
+      </c>
+      <c r="K79" s="3">
+        <v>4994</v>
+      </c>
+      <c r="L79" s="6">
+        <v>895274.30679999955</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17">
+      <c r="A80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80">
+        <v>2023</v>
+      </c>
+      <c r="E80" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" s="3">
+        <v>26747</v>
+      </c>
+      <c r="G80" s="3">
+        <v>2792</v>
+      </c>
+      <c r="H80" s="3">
+        <v>1213723.4799999993</v>
+      </c>
+      <c r="I80" s="3">
+        <v>796711.50796556519</v>
+      </c>
+      <c r="J80" s="3">
+        <v>6887</v>
+      </c>
+      <c r="K80" s="3">
+        <v>3986</v>
+      </c>
+      <c r="L80" s="6">
+        <v>814955.4035999995</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81">
+        <v>2023</v>
+      </c>
+      <c r="E81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F81" s="3">
+        <v>23831</v>
+      </c>
+      <c r="G81" s="3">
+        <v>2699</v>
+      </c>
+      <c r="H81" s="3">
+        <v>1040711.560000001</v>
+      </c>
+      <c r="I81" s="3">
+        <v>751750.40721751167</v>
+      </c>
+      <c r="J81" s="3">
+        <v>5754</v>
+      </c>
+      <c r="K81" s="3">
+        <v>3803</v>
+      </c>
+      <c r="L81" s="6">
+        <v>707348.18040000054</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82">
+        <v>2023</v>
+      </c>
+      <c r="E82" t="s">
+        <v>27</v>
+      </c>
+      <c r="F82" s="3">
+        <v>18413</v>
+      </c>
+      <c r="G82" s="3">
+        <v>2247</v>
+      </c>
+      <c r="H82" s="3">
+        <v>923989.20000000042</v>
+      </c>
+      <c r="I82" s="3">
+        <v>736832.21711679234</v>
+      </c>
+      <c r="J82" s="3">
+        <v>4988</v>
+      </c>
+      <c r="K82" s="3">
+        <v>3617</v>
+      </c>
+      <c r="L82" s="6">
+        <v>608029.60999999975</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83">
+        <v>2023</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83" s="3">
+        <v>17625</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2156</v>
+      </c>
+      <c r="H83" s="3">
+        <v>829479.0000000007</v>
+      </c>
+      <c r="I83" s="3">
+        <v>688742.24430320587</v>
+      </c>
+      <c r="J83" s="3">
+        <v>4503</v>
+      </c>
+      <c r="K83" s="3">
+        <v>3473</v>
+      </c>
+      <c r="L83" s="6">
+        <v>550085.75560000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="A84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84">
+        <v>2023</v>
+      </c>
+      <c r="E84" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84" s="3">
+        <v>20972</v>
+      </c>
+      <c r="G84" s="3">
+        <v>2965</v>
+      </c>
+      <c r="H84" s="3">
+        <v>1020750.7200000003</v>
+      </c>
+      <c r="I84" s="3">
+        <v>639941.58855046518</v>
+      </c>
+      <c r="J84" s="3">
+        <v>6393</v>
+      </c>
+      <c r="K84" s="3">
+        <v>3242</v>
+      </c>
+      <c r="L84" s="6">
+        <v>690405.58960000018</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="A85" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85">
+        <v>2023</v>
+      </c>
+      <c r="E85" t="s">
+        <v>30</v>
+      </c>
+      <c r="F85" s="3">
+        <v>33976</v>
+      </c>
+      <c r="G85" s="3">
+        <v>5138</v>
+      </c>
+      <c r="H85" s="3">
+        <v>1672448.639999998</v>
+      </c>
+      <c r="I85" s="3">
+        <v>1192025.4675103007</v>
+      </c>
+      <c r="J85" s="3">
+        <v>11615</v>
+      </c>
+      <c r="K85" s="3">
+        <v>7084</v>
+      </c>
+      <c r="L85" s="6">
+        <v>1094786.2748000005</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86">
+        <v>2023</v>
+      </c>
+      <c r="E86" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" s="3">
+        <v>26644</v>
+      </c>
+      <c r="G86" s="3">
+        <v>1776</v>
+      </c>
+      <c r="H86" s="3">
+        <v>717846.79999999993</v>
+      </c>
+      <c r="I86" s="3">
+        <v>416856.61039932823</v>
+      </c>
+      <c r="J86" s="3">
+        <v>3470</v>
+      </c>
+      <c r="K86" s="3">
+        <v>1623</v>
+      </c>
+      <c r="L86" s="6">
+        <v>515350.62720000005</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87">
+        <v>2023</v>
+      </c>
+      <c r="E87" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87" s="3">
+        <v>21319</v>
+      </c>
+      <c r="G87" s="3">
+        <v>1619</v>
+      </c>
+      <c r="H87" s="3">
+        <v>695259.52000000014</v>
+      </c>
+      <c r="I87" s="3">
+        <v>627232.48999117152</v>
+      </c>
+      <c r="J87" s="3">
+        <v>2890</v>
+      </c>
+      <c r="K87" s="3">
+        <v>2472</v>
+      </c>
+      <c r="L87" s="6">
+        <v>496930.46320000017</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
+      <c r="A88" t="s">
+        <v>0</v>
+      </c>
+      <c r="B88" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88">
+        <v>2023</v>
+      </c>
+      <c r="E88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88" s="3">
+        <v>27381</v>
+      </c>
+      <c r="G88" s="3">
+        <v>2183</v>
+      </c>
+      <c r="H88" s="3">
+        <v>878423</v>
+      </c>
+      <c r="I88" s="3">
+        <v>762155.52931046835</v>
+      </c>
+      <c r="J88" s="3">
+        <v>3658</v>
+      </c>
+      <c r="K88" s="3">
+        <v>3083</v>
+      </c>
+      <c r="L88" s="6">
+        <v>622914.84799999988</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89">
+        <v>2023</v>
+      </c>
+      <c r="E89" t="s">
+        <v>22</v>
+      </c>
+      <c r="F89" s="3">
+        <v>26524</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1833</v>
+      </c>
+      <c r="H89" s="3">
+        <v>758184.36000000022</v>
+      </c>
+      <c r="I89" s="3">
+        <v>641668.99086490355</v>
+      </c>
+      <c r="J89" s="3">
+        <v>3236</v>
+      </c>
+      <c r="K89" s="3">
+        <v>2496</v>
+      </c>
+      <c r="L89" s="6">
+        <v>553942.25119999994</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90">
+        <v>2023</v>
+      </c>
+      <c r="E90" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90" s="3">
+        <v>26931</v>
+      </c>
+      <c r="G90" s="3">
+        <v>1772</v>
+      </c>
+      <c r="H90" s="3">
+        <v>811417.40000000026</v>
+      </c>
+      <c r="I90" s="3">
+        <v>735838.28630223533</v>
+      </c>
+      <c r="J90" s="3">
+        <v>3167</v>
+      </c>
+      <c r="K90" s="3">
+        <v>2707</v>
+      </c>
+      <c r="L90" s="6">
+        <v>584191.54799999972</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91">
+        <v>2023</v>
+      </c>
+      <c r="E91" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="3">
+        <v>32146</v>
+      </c>
+      <c r="G91" s="3">
+        <v>2204</v>
+      </c>
+      <c r="H91" s="3">
+        <v>927267.76000000047</v>
+      </c>
+      <c r="I91" s="3">
+        <v>759573.60982263694</v>
+      </c>
+      <c r="J91" s="3">
+        <v>3997</v>
+      </c>
+      <c r="K91" s="3">
+        <v>3071</v>
+      </c>
+      <c r="L91" s="6">
+        <v>661646.51440000022</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92">
+        <v>2023</v>
+      </c>
+      <c r="E92" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" s="3">
+        <v>34631</v>
+      </c>
+      <c r="G92" s="3">
+        <v>2378</v>
+      </c>
+      <c r="H92" s="3">
+        <v>916442.96000000008</v>
+      </c>
+      <c r="I92" s="3">
+        <v>669302.64943875186</v>
+      </c>
+      <c r="J92" s="3">
+        <v>4043</v>
+      </c>
+      <c r="K92" s="3">
+        <v>2772</v>
+      </c>
+      <c r="L92" s="6">
+        <v>648669.47919999994</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" t="s">
+        <v>0</v>
+      </c>
+      <c r="B93" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93">
+        <v>2023</v>
+      </c>
+      <c r="E93" t="s">
+        <v>26</v>
+      </c>
+      <c r="F93" s="3">
+        <v>31828</v>
+      </c>
+      <c r="G93" s="3">
+        <v>2366</v>
+      </c>
+      <c r="H93" s="3">
+        <v>1067572.8</v>
+      </c>
+      <c r="I93" s="3">
+        <v>880795.89208997402</v>
+      </c>
+      <c r="J93" s="3">
+        <v>4788</v>
+      </c>
+      <c r="K93" s="3">
+        <v>3647</v>
+      </c>
+      <c r="L93" s="6">
+        <v>774449.41919999989</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" t="s">
+        <v>0</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94">
+        <v>2023</v>
+      </c>
+      <c r="E94" t="s">
+        <v>27</v>
+      </c>
+      <c r="F94" s="3">
+        <v>28687</v>
+      </c>
+      <c r="G94" s="3">
+        <v>2319</v>
+      </c>
+      <c r="H94" s="3">
+        <v>1087536.5999999999</v>
+      </c>
+      <c r="I94" s="3">
+        <v>977949.22152656654</v>
+      </c>
+      <c r="J94" s="3">
+        <v>4672</v>
+      </c>
+      <c r="K94" s="3">
+        <v>3855</v>
+      </c>
+      <c r="L94" s="6">
+        <v>785712.67840000021</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95">
+        <v>2023</v>
+      </c>
+      <c r="E95" t="s">
+        <v>28</v>
+      </c>
+      <c r="F95" s="3">
+        <v>26641</v>
+      </c>
+      <c r="G95" s="3">
+        <v>2083</v>
+      </c>
+      <c r="H95" s="3">
+        <v>996315.2799999998</v>
+      </c>
+      <c r="I95" s="3">
+        <v>858000.13701809349</v>
+      </c>
+      <c r="J95" s="3">
+        <v>4246</v>
+      </c>
+      <c r="K95" s="3">
+        <v>3370</v>
+      </c>
+      <c r="L95" s="6">
+        <v>705020.73199999984</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96">
+        <v>2023</v>
+      </c>
+      <c r="E96" t="s">
+        <v>29</v>
+      </c>
+      <c r="F96" s="3">
+        <v>35701</v>
+      </c>
+      <c r="G96" s="3">
+        <v>2491</v>
+      </c>
+      <c r="H96" s="3">
+        <v>1104100.0799999996</v>
+      </c>
+      <c r="I96" s="3">
+        <v>911134.62697026751</v>
+      </c>
+      <c r="J96" s="3">
+        <v>5076</v>
+      </c>
+      <c r="K96" s="3">
+        <v>3791</v>
+      </c>
+      <c r="L96" s="6">
+        <v>815157.64519999991</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
+      <c r="A97" t="s">
+        <v>0</v>
+      </c>
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97">
+        <v>2023</v>
+      </c>
+      <c r="E97" t="s">
+        <v>30</v>
+      </c>
+      <c r="F97" s="3">
+        <v>57584</v>
+      </c>
+      <c r="G97" s="3">
+        <v>4726</v>
+      </c>
+      <c r="H97" s="3">
+        <v>1980792.7600000005</v>
+      </c>
+      <c r="I97" s="3">
+        <v>1600422.0416956265</v>
+      </c>
+      <c r="J97" s="3">
+        <v>9749</v>
+      </c>
+      <c r="K97" s="3">
+        <v>7071</v>
+      </c>
+      <c r="L97" s="6">
+        <v>1453847.8672</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
+      <c r="A98" t="s">
+        <v>0</v>
+      </c>
+      <c r="B98" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98">
+        <v>2023</v>
+      </c>
+      <c r="E98" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" s="3">
+        <v>10423</v>
+      </c>
+      <c r="G98" s="3">
+        <v>2131</v>
+      </c>
+      <c r="H98" s="3">
+        <v>649125.76000000094</v>
+      </c>
+      <c r="I98" s="3">
+        <v>41715.79914922014</v>
+      </c>
+      <c r="J98" s="3">
+        <v>7157</v>
+      </c>
+      <c r="K98" s="3">
+        <v>432</v>
+      </c>
+      <c r="L98" s="6">
+        <v>243799.12119999979</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
+      <c r="A99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99">
+        <v>2023</v>
+      </c>
+      <c r="E99" t="s">
+        <v>20</v>
+      </c>
+      <c r="F99" s="3">
+        <v>9033</v>
+      </c>
+      <c r="G99" s="3">
+        <v>2028</v>
+      </c>
+      <c r="H99" s="3">
+        <v>636097.72000000032</v>
+      </c>
+      <c r="I99" s="3">
+        <v>19141.852741454648</v>
+      </c>
+      <c r="J99" s="3">
+        <v>7130</v>
+      </c>
+      <c r="K99" s="3">
+        <v>287</v>
+      </c>
+      <c r="L99" s="6">
+        <v>238534.16840000008</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
+      <c r="A100" t="s">
+        <v>0</v>
+      </c>
+      <c r="B100" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100">
+        <v>2023</v>
+      </c>
+      <c r="E100" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" s="3">
+        <v>10851</v>
+      </c>
+      <c r="G100" s="3">
+        <v>2303</v>
+      </c>
+      <c r="H100" s="3">
+        <v>708687.04000000108</v>
+      </c>
+      <c r="I100" s="3">
+        <v>17271.650152198017</v>
+      </c>
+      <c r="J100" s="3">
+        <v>6673</v>
+      </c>
+      <c r="K100" s="3">
+        <v>264</v>
+      </c>
+      <c r="L100" s="6">
+        <v>267327.14439999964</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B101" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101">
+        <v>2023</v>
+      </c>
+      <c r="E101" t="s">
+        <v>22</v>
+      </c>
+      <c r="F101" s="3">
+        <v>9399</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1882</v>
+      </c>
+      <c r="H101" s="3">
+        <v>504473.12000000075</v>
+      </c>
+      <c r="I101" s="3">
+        <v>26584.266785866916</v>
+      </c>
+      <c r="J101" s="3">
+        <v>5430</v>
+      </c>
+      <c r="K101" s="3">
+        <v>293</v>
+      </c>
+      <c r="L101" s="6">
+        <v>183978.40199999997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>0</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102">
+        <v>2023</v>
+      </c>
+      <c r="E102" t="s">
+        <v>23</v>
+      </c>
+      <c r="F102" s="3">
+        <v>9119</v>
+      </c>
+      <c r="G102" s="3">
+        <v>2290</v>
+      </c>
+      <c r="H102" s="3">
+        <v>652217.84000000032</v>
+      </c>
+      <c r="I102" s="3">
+        <v>32593.445356558812</v>
+      </c>
+      <c r="J102" s="3">
+        <v>7664</v>
+      </c>
+      <c r="K102" s="3">
+        <v>331</v>
+      </c>
+      <c r="L102" s="6">
+        <v>243744.68359999984</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103">
+        <v>2023</v>
+      </c>
+      <c r="E103" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" s="3">
+        <v>11768</v>
+      </c>
+      <c r="G103" s="3">
+        <v>2975</v>
+      </c>
+      <c r="H103" s="3">
+        <v>855303.6</v>
+      </c>
+      <c r="I103" s="3">
+        <v>49903.862929742521</v>
+      </c>
+      <c r="J103" s="3">
+        <v>10822</v>
+      </c>
+      <c r="K103" s="3">
+        <v>525</v>
+      </c>
+      <c r="L103" s="6">
+        <v>325635.23879999993</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="A104" t="s">
+        <v>0</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104">
+        <v>2023</v>
+      </c>
+      <c r="E104" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" s="3">
+        <v>10696</v>
+      </c>
+      <c r="G104" s="3">
+        <v>2667</v>
+      </c>
+      <c r="H104" s="3">
+        <v>821730.9600000002</v>
+      </c>
+      <c r="I104" s="3">
+        <v>44962.722369537114</v>
+      </c>
+      <c r="J104" s="3">
+        <v>8436</v>
+      </c>
+      <c r="K104" s="3">
+        <v>465</v>
+      </c>
+      <c r="L104" s="6">
+        <v>308061.962</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="A105" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105">
+        <v>2023</v>
+      </c>
+      <c r="E105" t="s">
+        <v>26</v>
+      </c>
+      <c r="F105" s="3">
+        <v>12003</v>
+      </c>
+      <c r="G105" s="3">
+        <v>2671</v>
+      </c>
+      <c r="H105" s="3">
+        <v>808569.24000000069</v>
+      </c>
+      <c r="I105" s="3">
+        <v>35929.278625000254</v>
+      </c>
+      <c r="J105" s="3">
+        <v>8256</v>
+      </c>
+      <c r="K105" s="3">
+        <v>420</v>
+      </c>
+      <c r="L105" s="6">
+        <v>309121.34840000008</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
+      <c r="A106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106">
+        <v>2023</v>
+      </c>
+      <c r="E106" t="s">
+        <v>27</v>
+      </c>
+      <c r="F106" s="3">
+        <v>10681</v>
+      </c>
+      <c r="G106" s="3">
+        <v>2613</v>
+      </c>
+      <c r="H106" s="3">
+        <v>788953.23999999894</v>
+      </c>
+      <c r="I106" s="3">
+        <v>20462.827829075984</v>
+      </c>
+      <c r="J106" s="3">
+        <v>9430</v>
+      </c>
+      <c r="K106" s="3">
+        <v>264</v>
+      </c>
+      <c r="L106" s="6">
+        <v>294642.84960000002</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
+      <c r="A107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107">
+        <v>2023</v>
+      </c>
+      <c r="E107" t="s">
+        <v>28</v>
+      </c>
+      <c r="F107" s="3">
+        <v>9644</v>
+      </c>
+      <c r="G107" s="3">
+        <v>2401</v>
+      </c>
+      <c r="H107" s="3">
+        <v>666011</v>
+      </c>
+      <c r="I107" s="3">
+        <v>30352.237345987829</v>
+      </c>
+      <c r="J107" s="3">
+        <v>7536</v>
+      </c>
+      <c r="K107" s="3">
+        <v>299</v>
+      </c>
+      <c r="L107" s="6">
+        <v>249296.56360000011</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
+      <c r="A108" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108">
+        <v>2023</v>
+      </c>
+      <c r="E108" t="s">
+        <v>29</v>
+      </c>
+      <c r="F108" s="3">
+        <v>12847</v>
+      </c>
+      <c r="G108" s="3">
+        <v>3133</v>
+      </c>
+      <c r="H108" s="3">
+        <v>887652.03999999922</v>
+      </c>
+      <c r="I108" s="3">
+        <v>32907.242987257465</v>
+      </c>
+      <c r="J108" s="3">
+        <v>10879</v>
+      </c>
+      <c r="K108" s="3">
+        <v>485</v>
+      </c>
+      <c r="L108" s="6">
+        <v>334095.30680000025</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
+      <c r="A109" t="s">
+        <v>0</v>
+      </c>
+      <c r="B109" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109">
+        <v>2023</v>
+      </c>
+      <c r="E109" t="s">
+        <v>30</v>
+      </c>
+      <c r="F109" s="3">
+        <v>24582</v>
+      </c>
+      <c r="G109" s="3">
+        <v>6235</v>
+      </c>
+      <c r="H109" s="3">
+        <v>1628494.479999996</v>
+      </c>
+      <c r="I109" s="3">
+        <v>74274.764113856494</v>
+      </c>
+      <c r="J109" s="3">
+        <v>18389</v>
+      </c>
+      <c r="K109" s="3">
+        <v>784</v>
+      </c>
+      <c r="L109" s="6">
+        <v>630162.61320000025</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K70" xr:uid="{405DFD03-4F9B-482B-9B5A-511F39FADA19}"/>
+  <autoFilter ref="A1:K73" xr:uid="{405DFD03-4F9B-482B-9B5A-511F39FADA19}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="2024"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
